--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>130132614</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>130132614</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>130132614</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34266-2025 artfynd.xlsx
+++ b/artfynd/A 34266-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>130132598</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
